--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N47_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N47_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>12.46650523924278</v>
+        <v>2.025807101376952</v>
       </c>
       <c r="D2" t="n">
-        <v>11.90716147922019</v>
+        <v>1.93491374037328</v>
       </c>
       <c r="E2" t="n">
-        <v>17.5085060669492</v>
+        <v>2.845132235879245</v>
       </c>
       <c r="F2" t="n">
-        <v>17.81604242166598</v>
+        <v>2.895106893520722</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>43.1004896262893</v>
+        <v>7.003829564272011</v>
       </c>
       <c r="D3" t="n">
-        <v>42.5726838572889</v>
+        <v>6.918061126809446</v>
       </c>
       <c r="E3" t="n">
-        <v>17.5085060669492</v>
+        <v>2.845132235879245</v>
       </c>
       <c r="F3" t="n">
-        <v>17.81604242166598</v>
+        <v>2.895106893520722</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>26.51730964177815</v>
+        <v>4.30906281678895</v>
       </c>
       <c r="D4" t="n">
-        <v>26.56934015884991</v>
+        <v>4.31751777581311</v>
       </c>
       <c r="E4" t="n">
-        <v>17.5085060669492</v>
+        <v>2.845132235879245</v>
       </c>
       <c r="F4" t="n">
-        <v>17.81604242166598</v>
+        <v>2.895106893520722</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>25.20257366635133</v>
+        <v>4.095418220782092</v>
       </c>
       <c r="D5" t="n">
-        <v>24.14981982673452</v>
+        <v>3.924345721844359</v>
       </c>
       <c r="E5" t="n">
-        <v>17.5085060669492</v>
+        <v>2.845132235879245</v>
       </c>
       <c r="F5" t="n">
-        <v>17.81604242166598</v>
+        <v>2.895106893520722</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>16.33584807569059</v>
+        <v>2.654575312299721</v>
       </c>
       <c r="D6" t="n">
-        <v>15.30383634500688</v>
+        <v>2.486873406063619</v>
       </c>
       <c r="E6" t="n">
-        <v>17.5085060669492</v>
+        <v>2.845132235879245</v>
       </c>
       <c r="F6" t="n">
-        <v>17.81604242166598</v>
+        <v>2.895106893520722</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>32.56351242717231</v>
+        <v>5.2915707694155</v>
       </c>
       <c r="D7" t="n">
-        <v>31.42406835968463</v>
+        <v>5.106411108448753</v>
       </c>
       <c r="E7" t="n">
-        <v>17.5085060669492</v>
+        <v>2.845132235879245</v>
       </c>
       <c r="F7" t="n">
-        <v>17.81604242166598</v>
+        <v>2.895106893520722</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>8.01682790303269</v>
+        <v>1.302734534242812</v>
       </c>
       <c r="D8" t="n">
-        <v>7.651688941988062</v>
+        <v>1.24339945307306</v>
       </c>
       <c r="E8" t="n">
-        <v>17.5085060669492</v>
+        <v>2.845132235879245</v>
       </c>
       <c r="F8" t="n">
-        <v>17.81604242166598</v>
+        <v>2.895106893520722</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>48.95524592764384</v>
+        <v>7.955227463242124</v>
       </c>
       <c r="D9" t="n">
-        <v>48.26162173404619</v>
+        <v>7.842513531782507</v>
       </c>
       <c r="E9" t="n">
-        <v>17.5085060669492</v>
+        <v>2.845132235879245</v>
       </c>
       <c r="F9" t="n">
-        <v>17.81604242166598</v>
+        <v>2.895106893520722</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>37.98507257953557</v>
+        <v>6.17257429417453</v>
       </c>
       <c r="D10" t="n">
-        <v>39.12600957783641</v>
+        <v>6.357976556398416</v>
       </c>
       <c r="E10" t="n">
-        <v>17.5085060669492</v>
+        <v>2.845132235879245</v>
       </c>
       <c r="F10" t="n">
-        <v>17.81604242166598</v>
+        <v>2.895106893520722</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>40.85542037366745</v>
+        <v>6.639005810720961</v>
       </c>
       <c r="D11" t="n">
-        <v>41.99658302621549</v>
+        <v>6.824444741760018</v>
       </c>
       <c r="E11" t="n">
-        <v>17.5085060669492</v>
+        <v>2.845132235879245</v>
       </c>
       <c r="F11" t="n">
-        <v>17.81604242166598</v>
+        <v>2.895106893520722</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>62.65974269194957</v>
+        <v>10.18220818744181</v>
       </c>
       <c r="D12" t="n">
-        <v>62.22826383649778</v>
+        <v>10.11209287343089</v>
       </c>
       <c r="E12" t="n">
-        <v>17.5085060669492</v>
+        <v>2.845132235879245</v>
       </c>
       <c r="F12" t="n">
-        <v>17.81604242166598</v>
+        <v>2.895106893520722</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>52.60841709357508</v>
+        <v>8.548867777705951</v>
       </c>
       <c r="D13" t="n">
-        <v>53.67459225170071</v>
+        <v>8.722121240901366</v>
       </c>
       <c r="E13" t="n">
-        <v>17.5085060669492</v>
+        <v>2.845132235879245</v>
       </c>
       <c r="F13" t="n">
-        <v>17.81604242166598</v>
+        <v>2.895106893520722</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>60.52482712454443</v>
+        <v>9.83528440773847</v>
       </c>
       <c r="D14" t="n">
-        <v>60.56362852391232</v>
+        <v>9.841589635135753</v>
       </c>
       <c r="E14" t="n">
-        <v>17.5085060669492</v>
+        <v>2.845132235879245</v>
       </c>
       <c r="F14" t="n">
-        <v>17.81604242166598</v>
+        <v>2.895106893520722</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>59.5565480061213</v>
+        <v>9.677939050994711</v>
       </c>
       <c r="D15" t="n">
-        <v>59.88559119003231</v>
+        <v>9.73140856838025</v>
       </c>
       <c r="E15" t="n">
-        <v>17.5085060669492</v>
+        <v>2.845132235879245</v>
       </c>
       <c r="F15" t="n">
-        <v>17.81604242166598</v>
+        <v>2.895106893520722</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
